--- a/testcase_new/s3/java/暂时屏蔽用例记录表.xlsx
+++ b/testcase_new/s3/java/暂时屏蔽用例记录表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>屏蔽原因</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,6 +39,18 @@
   </si>
   <si>
     <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateObject18585</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TestAllowReput18594</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateSameBucket18614</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -510,27 +522,39 @@
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6">
@@ -639,6 +663,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -651,13 +682,6 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testcase_new/s3/java/暂时屏蔽用例记录表.xlsx
+++ b/testcase_new/s3/java/暂时屏蔽用例记录表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>屏蔽原因</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,6 +51,50 @@
   </si>
   <si>
     <t>CreateSameBucket18614</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18682</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18683</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18684</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18705</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18688</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18689</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18690</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18691</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18694</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18762</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UploadPart18763</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -82,7 +126,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -105,14 +149,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -477,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="5" max="5" width="36.625" customWidth="1"/>
@@ -558,91 +648,135 @@
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F9" s="1"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="1"/>
+      <c r="A10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F17" s="1"/>
     </row>
     <row r="18" spans="1:6">
@@ -653,24 +787,9 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A12:D12"/>
+  <mergeCells count="18">
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
@@ -681,7 +800,13 @@
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
